--- a/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,2</t>
+          <t>-0,0; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,22</t>
+          <t>-0,48; 5,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,8</t>
+          <t>-2,61; 2,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,47</t>
+          <t>-5,83; 0,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 213,96</t>
+          <t>-1,61; 206,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 120,31</t>
+          <t>-9,21; 112,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 52,37</t>
+          <t>-31,98; 50,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 4,05</t>
+          <t>-39,85; 6,99</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,57</t>
+          <t>-1,81; 2,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,73</t>
+          <t>-0,95; 4,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,46</t>
+          <t>-0,01; 4,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 9,53</t>
+          <t>0,14; 8,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 57,56</t>
+          <t>-27,05; 61,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 70,92</t>
+          <t>-9,77; 63,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 112,93</t>
+          <t>-1,23; 108,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 174,82</t>
+          <t>-0,14; 145,07</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,66</t>
+          <t>-2,45; 2,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,93</t>
+          <t>-1,99; 4,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,88</t>
+          <t>-0,07; 4,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 48,71</t>
+          <t>-2,68; 52,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 61,55</t>
+          <t>-33,06; 61,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 64,54</t>
+          <t>-22,42; 69,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 174,72</t>
+          <t>-1,88; 194,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 433,13</t>
+          <t>-20,72; 481,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,61</t>
+          <t>0,04; 4,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,92</t>
+          <t>-0,54; 4,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,36</t>
+          <t>-1,51; 3,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,76</t>
+          <t>-2,51; 2,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 105,5</t>
+          <t>0,24; 98,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 76,08</t>
+          <t>-6,66; 73,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 57,98</t>
+          <t>-18,71; 61,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 40,04</t>
+          <t>-26,37; 38,32</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,35</t>
+          <t>0,13; 2,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,02</t>
+          <t>0,31; 3,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,56</t>
+          <t>0,12; 2,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 21,24</t>
+          <t>-0,22; 21,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 53,59</t>
+          <t>2,07; 52,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 45,39</t>
+          <t>3,63; 47,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 51,15</t>
+          <t>1,35; 50,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 212,75</t>
+          <t>-2,36; 250,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-18,38%</t>
+          <t>-10,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,22</t>
+          <t>0,31; 4,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,2</t>
+          <t>-0,49; 5,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,84</t>
+          <t>-2,64; 2,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 0,79</t>
+          <t>-4,36; 1,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 206,86</t>
+          <t>5,62; 195,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 112,55</t>
+          <t>-7,39; 119,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 50,15</t>
+          <t>-32,5; 49,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 6,99</t>
+          <t>-31,02; 16,04</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,68</t>
+          <t>-1,92; 2,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,44</t>
+          <t>-0,93; 4,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,42</t>
+          <t>-0,09; 4,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 8,58</t>
+          <t>-1,15; 4,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 61,38</t>
+          <t>-28,77; 52,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 63,35</t>
+          <t>-10,55; 65,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 108,78</t>
+          <t>-2,56; 103,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 145,07</t>
+          <t>-8,82; 42,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>143,37%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,73</t>
+          <t>-2,45; 2,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,09</t>
+          <t>-1,96; 4,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,14</t>
+          <t>-0,36; 4,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 52,46</t>
+          <t>-3,0; 3,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 61,06</t>
+          <t>-35,32; 64,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 69,54</t>
+          <t>-22,29; 70,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 194,37</t>
+          <t>-11,77; 182,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 481,37</t>
+          <t>-21,89; 35,53</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,51</t>
+          <t>0,22; 4,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,79</t>
+          <t>-0,78; 4,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,62</t>
+          <t>-1,75; 3,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,68</t>
+          <t>-0,69; 3,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 98,99</t>
+          <t>3,07; 98,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 73,8</t>
+          <t>-9,67; 73,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 61,76</t>
+          <t>-21,77; 59,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 38,32</t>
+          <t>-8,27; 55,47</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,4</t>
+          <t>0,04; 2,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,19</t>
+          <t>0,51; 3,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,6</t>
+          <t>0,18; 2,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 21,97</t>
+          <t>-0,95; 1,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 52,83</t>
+          <t>0,69; 54,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 47,04</t>
+          <t>6,25; 48,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 50,72</t>
+          <t>3,05; 51,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 250,37</t>
+          <t>-8,17; 18,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
